--- a/Lab 1/RV32I_Table.xlsx
+++ b/Lab 1/RV32I_Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\OneDrive\Desktop\CA Lab\Experiment 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\OneDrive\Desktop\CA Lab\Lab 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D29EE8A-A6E0-4523-96DA-EA5F579D18BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66945B1B-F0AB-42FF-8A02-94C1503CE64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="101">
   <si>
     <t>OPCODE ENCODINGS</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>pass b</t>
+  </si>
+  <si>
+    <t>4'b1001</t>
   </si>
 </sst>
 </file>
@@ -1138,10 +1144,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -1180,10 +1186,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>44</v>
@@ -1758,13 +1764,13 @@
         <v>56</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="19.2" x14ac:dyDescent="0.35">
@@ -1914,13 +1920,13 @@
         <v>36</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="5:14" ht="19.2" x14ac:dyDescent="0.35">
@@ -1944,13 +1950,13 @@
         <v>36</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="5:14" ht="19.2" x14ac:dyDescent="0.35">
@@ -1974,13 +1980,13 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="5:14" ht="19.2" x14ac:dyDescent="0.35">
@@ -2004,13 +2010,13 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="5:14" ht="19.2" x14ac:dyDescent="0.35">
@@ -2034,13 +2040,13 @@
         <v>36</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="5:14" ht="19.2" x14ac:dyDescent="0.35">
@@ -2064,13 +2070,13 @@
         <v>36</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="5:14" ht="19.2" x14ac:dyDescent="0.35">
